--- a/docs/Blue365_QMS_업데이트_양식.xlsx
+++ b/docs/Blue365_QMS_업데이트_양식.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="생료" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="원료" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="클링커" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시멘트" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="물성" sheetId="5" state="visible" r:id="rId5"/>
@@ -500,7 +500,7 @@
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1) LIMS(품질관리)에서 공정별 결과를 엑셀로 내려받습니다 — 생료, 클링커, 시멘트(분쇄), 제품(출하).</t>
+          <t xml:space="preserve">  1) LIMS(품질관리)에서 공정별 결과를 엑셀로 내려받습니다 — 원료, 클링커, 시멘트(분쇄), 제품(출하).</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · 생료 / 클링커 / 시멘트 / 물성 / 클링커일일  →  공정 모니터링 · 그래프 보기 · SPC · 원인 진단 · 강도 예측 · 배합 설계 · 6가크롬</t>
+          <t xml:space="preserve">  · 원료 / 클링커 / 시멘트 / 물성 / 클링커일일  →  공정 모니터링 · 그래프 보기 · SPC · 원인 진단 · 강도 예측 · 배합 설계 · 6가크롬</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '생료·클링커·클링커일일'은 형태를 보여주기 위한 예시(추정)입니다. 실제 값으로 바꿔 쓰세요.</t>
+          <t xml:space="preserve">   '원료·클링커·클링커일일'은 형태를 보여주기 위한 예시(추정)입니다. 실제 값으로 바꿔 쓰세요.</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>※ 예시(추정) — 생료(킬른 피드) XRF. 실제 LIMS 생료 결과로 바꿔 쓰세요. 90㎛·200㎛는 체 잔사(%).</t>
+          <t>※ 예시(추정) — 원료(킬른 피드) XRF. 실제 LIMS 원료 결과로 바꿔 쓰세요. 90㎛·200㎛는 체 잔사(%).</t>
         </is>
       </c>
     </row>
@@ -12040,7 +12040,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -12050,12 +12050,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>생료(킬른 피드) 화학·분말도</t>
+          <t>원료(킬른 피드) 화학·분말도</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>LIMS 생료 결과</t>
+          <t>LIMS 원료 결과</t>
         </is>
       </c>
     </row>

--- a/docs/Blue365_QMS_업데이트_양식.xlsx
+++ b/docs/Blue365_QMS_업데이트_양식.xlsx
@@ -34502,7 +34502,7 @@
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>사용자 지정(킬른 5기: 3K~7K)</t>
+          <t>사용자 지정(킬른 5기: 3K~7K). LIMS 표기 SA1KL3 = 3K 로 읽음</t>
         </is>
       </c>
     </row>
